--- a/Excel/InfiniteModelConfig.xlsx
+++ b/Excel/InfiniteModelConfig.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -30,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
   <si>
     <t>ID</t>
   </si>
@@ -59,64 +64,67 @@
     <t>血量</t>
   </si>
   <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>1000</t>
+    <t>1001</t>
+  </si>
+  <si>
+    <t>200</t>
   </si>
   <si>
     <t>防御</t>
   </si>
   <si>
-    <t>2002</t>
+    <t>1002</t>
+  </si>
+  <si>
+    <t>150</t>
   </si>
   <si>
     <t>攻击</t>
   </si>
   <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>200</t>
+    <t>1003</t>
+  </si>
+  <si>
+    <t>50</t>
   </si>
   <si>
     <t>闪避</t>
   </si>
   <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>50</t>
+    <t>14</t>
   </si>
   <si>
     <t>速度</t>
   </si>
   <si>
-    <t>6</t>
+    <t>11</t>
+  </si>
+  <si>
+    <t>100</t>
   </si>
   <si>
     <t>精准</t>
   </si>
   <si>
-    <t>32</t>
+    <t>13</t>
   </si>
   <si>
     <t>坦克</t>
   </si>
   <si>
-    <t>2003,2002</t>
-  </si>
-  <si>
-    <t>1000,1000</t>
+    <t>1001,1002</t>
+  </si>
+  <si>
+    <t>3000,200</t>
   </si>
   <si>
     <t>战士</t>
   </si>
   <si>
-    <t>2003,2001</t>
-  </si>
-  <si>
-    <t>1000,200</t>
+    <t>1002,1003</t>
+  </si>
+  <si>
+    <t>200,100</t>
   </si>
   <si>
     <t>刺客</t>
@@ -131,7 +139,7 @@
     <t>影舞者</t>
   </si>
   <si>
-    <t>31,32</t>
+    <t>13,14</t>
   </si>
   <si>
     <t>50,50</t>
@@ -782,12 +790,12 @@
     <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
@@ -1193,8 +1201,8 @@
       <c r="M3" s="5"/>
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="1:17">
       <c r="A4" s="2"/>
@@ -1220,8 +1228,8 @@
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:17">
       <c r="A5" s="2"/>
@@ -1247,14 +1255,14 @@
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
     </row>
-    <row r="6" customHeight="1" spans="3:17">
+    <row r="6" customHeight="1" spans="1:17">
       <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="11" t="s">
@@ -1263,19 +1271,19 @@
       <c r="F6" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
       <c r="L6" s="10"/>
       <c r="M6" s="10"/>
       <c r="N6" s="10"/>
       <c r="O6" s="10"/>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="8"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
     </row>
-    <row r="7" customHeight="1" spans="3:17">
+    <row r="7" customHeight="1" spans="1:17">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1286,71 +1294,71 @@
         <v>12</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
+        <v>13</v>
+      </c>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
       <c r="L7" s="10"/>
       <c r="M7" s="10"/>
       <c r="N7" s="10"/>
       <c r="O7" s="10"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
     </row>
-    <row r="8" customHeight="1" spans="3:17">
+    <row r="8" customHeight="1" spans="1:17">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
+        <v>16</v>
+      </c>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
       <c r="L8" s="10"/>
       <c r="M8" s="10"/>
       <c r="N8" s="10"/>
       <c r="O8" s="10"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
     </row>
-    <row r="9" customHeight="1" spans="3:17">
+    <row r="9" customHeight="1" spans="1:17">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
       <c r="L9" s="10"/>
       <c r="M9" s="10"/>
       <c r="N9" s="10"/>
       <c r="O9" s="10"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
     </row>
-    <row r="10" customHeight="1" spans="3:6">
+    <row r="10" customHeight="1" spans="1:17">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1361,82 +1369,82 @@
         <v>20</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="3:6">
+    <row r="11" customHeight="1" spans="1:17">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="3:6">
+    <row r="12" customHeight="1" spans="1:17">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="3:6">
+    <row r="13" customHeight="1" spans="1:17">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="3:6">
+    <row r="14" customHeight="1" spans="1:17">
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="3:6">
+    <row r="15" customHeight="1" spans="1:17">
       <c r="C15" s="1">
         <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 E3 F3 G3 H3 I3 D4 E4 F4 G4 H4 I4 C5 D5 E5 F5 G5 H5 I5 J5 K5 L5 M5 N5 O5 C3:C4 J3:J4 K3:K4 L3:L4 M3:M4 N3:N4 O3:O4" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:O5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
